--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2022_T2_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2022_T2_2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="77">
   <si>
     <t/>
   </si>
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>57</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,64 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.15e+05</t>
-  </si>
-  <si>
-    <t>(78592.918)</t>
-  </si>
-  <si>
-    <t>494.816</t>
-  </si>
-  <si>
-    <t>(37.499)</t>
-  </si>
-  <si>
-    <t>3.709</t>
-  </si>
-  <si>
-    <t>(0.047)</t>
-  </si>
-  <si>
-    <t>7.431</t>
-  </si>
-  <si>
-    <t>(1.504)</t>
-  </si>
-  <si>
-    <t>87.121</t>
-  </si>
-  <si>
-    <t>(0.501)</t>
-  </si>
-  <si>
-    <t>9.05e+05</t>
-  </si>
-  <si>
-    <t>(54154.347)</t>
-  </si>
-  <si>
-    <t>2.186</t>
-  </si>
-  <si>
-    <t>(0.131)</t>
-  </si>
-  <si>
-    <t>2.534</t>
-  </si>
-  <si>
-    <t>(0.413)</t>
-  </si>
-  <si>
-    <t>29.793</t>
-  </si>
-  <si>
-    <t>(4.382)</t>
-  </si>
-  <si>
-    <t>0.931</t>
-  </si>
-  <si>
-    <t>(0.034)</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -138,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>7.13e+05</t>
-  </si>
-  <si>
-    <t>(1.03e+05)</t>
-  </si>
-  <si>
-    <t>490.454</t>
-  </si>
-  <si>
-    <t>(44.975)</t>
-  </si>
-  <si>
-    <t>3.327</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>24.621</t>
-  </si>
-  <si>
-    <t>(3.277)</t>
-  </si>
-  <si>
-    <t>91.548</t>
-  </si>
-  <si>
-    <t>(0.378)</t>
-  </si>
-  <si>
-    <t>1.39e+06</t>
-  </si>
-  <si>
-    <t>(58842.783)</t>
-  </si>
-  <si>
-    <t>3.369</t>
-  </si>
-  <si>
-    <t>(0.122)</t>
-  </si>
-  <si>
-    <t>6.000</t>
-  </si>
-  <si>
-    <t>(0.561)</t>
-  </si>
-  <si>
-    <t>44.207</t>
-  </si>
-  <si>
-    <t>(2.781)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -213,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.97e+05</t>
-  </si>
-  <si>
-    <t>-4.362</t>
-  </si>
-  <si>
-    <t>-0.381***</t>
-  </si>
-  <si>
-    <t>17.190***</t>
-  </si>
-  <si>
-    <t>4.427***</t>
-  </si>
-  <si>
-    <t>4.84e+05***</t>
-  </si>
-  <si>
-    <t>1.183***</t>
-  </si>
-  <si>
-    <t>3.466***</t>
-  </si>
-  <si>
-    <t>14.414***</t>
-  </si>
-  <si>
-    <t>0.069**</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>
@@ -301,13 +304,13 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2">
@@ -324,13 +327,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -353,7 +356,7 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -367,16 +370,16 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -393,7 +396,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -413,16 +416,16 @@
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -439,7 +442,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -459,16 +462,16 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -485,7 +488,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -505,16 +508,16 @@
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -531,7 +534,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -551,16 +554,16 @@
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -577,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -597,16 +600,16 @@
         <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -623,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
@@ -643,16 +646,16 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -669,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s">
         <v>0</v>
@@ -689,16 +692,16 @@
         <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -715,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
@@ -735,16 +738,16 @@
         <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -761,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
         <v>0</v>
@@ -781,16 +784,16 @@
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
@@ -807,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F23" t="s">
         <v>0</v>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2022_T2_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2022_T2_2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="76">
   <si>
     <t/>
   </si>
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>58</t>
+  </si>
+  <si>
+    <t>57</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,127 +72,124 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
+    <t>5.15e+05</t>
+  </si>
+  <si>
+    <t>(78592.918)</t>
+  </si>
+  <si>
+    <t>494.816</t>
+  </si>
+  <si>
+    <t>(37.499)</t>
+  </si>
+  <si>
+    <t>3.709</t>
+  </si>
+  <si>
+    <t>(0.047)</t>
+  </si>
+  <si>
+    <t>7.431</t>
+  </si>
+  <si>
+    <t>(1.504)</t>
+  </si>
+  <si>
+    <t>87.121</t>
+  </si>
+  <si>
+    <t>(0.501)</t>
+  </si>
+  <si>
+    <t>9.05e+05</t>
+  </si>
+  <si>
+    <t>(54154.347)</t>
+  </si>
+  <si>
+    <t>2.186</t>
+  </si>
+  <si>
+    <t>(0.131)</t>
+  </si>
+  <si>
+    <t>2.534</t>
+  </si>
+  <si>
+    <t>(0.413)</t>
+  </si>
+  <si>
+    <t>29.793</t>
+  </si>
+  <si>
+    <t>(4.382)</t>
+  </si>
+  <si>
+    <t>0.931</t>
+  </si>
+  <si>
+    <t>(0.034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (2) </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>7.13e+05</t>
+  </si>
+  <si>
+    <t>(1.03e+05)</t>
+  </si>
+  <si>
+    <t>490.454</t>
+  </si>
+  <si>
+    <t>(44.975)</t>
+  </si>
+  <si>
+    <t>3.327</t>
   </si>
   <si>
     <t>(0.049)</t>
   </si>
   <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (2) </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>24.621</t>
+  </si>
+  <si>
+    <t>(3.277)</t>
+  </si>
+  <si>
+    <t>91.548</t>
+  </si>
+  <si>
+    <t>(0.378)</t>
+  </si>
+  <si>
+    <t>1.39e+06</t>
+  </si>
+  <si>
+    <t>(58842.783)</t>
+  </si>
+  <si>
+    <t>3.369</t>
+  </si>
+  <si>
+    <t>(0.122)</t>
+  </si>
+  <si>
+    <t>6.000</t>
+  </si>
+  <si>
+    <t>(0.561)</t>
+  </si>
+  <si>
+    <t>44.207</t>
+  </si>
+  <si>
+    <t>(2.781)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +213,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.97e+05</t>
+  </si>
+  <si>
+    <t>-4.362</t>
+  </si>
+  <si>
+    <t>-0.381***</t>
+  </si>
+  <si>
+    <t>17.190***</t>
+  </si>
+  <si>
+    <t>4.427***</t>
+  </si>
+  <si>
+    <t>4.84e+05***</t>
+  </si>
+  <si>
+    <t>1.183***</t>
+  </si>
+  <si>
+    <t>3.466***</t>
+  </si>
+  <si>
+    <t>14.414***</t>
+  </si>
+  <si>
+    <t>0.069**</t>
   </si>
 </sst>
 </file>
@@ -304,13 +301,13 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2">
@@ -327,13 +324,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -356,7 +353,7 @@
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -370,16 +367,16 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -396,7 +393,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -416,16 +413,16 @@
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -442,7 +439,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -462,16 +459,16 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -488,7 +485,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -508,16 +505,16 @@
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -534,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -554,16 +551,16 @@
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -580,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -600,16 +597,16 @@
         <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
@@ -626,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
@@ -646,16 +643,16 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -672,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F17" t="s">
         <v>0</v>
@@ -692,16 +689,16 @@
         <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -718,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
         <v>0</v>
@@ -738,16 +735,16 @@
         <v>35</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
@@ -764,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
         <v>0</v>
@@ -784,16 +781,16 @@
         <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23">
@@ -810,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F23" t="s">
         <v>0</v>
